--- a/FP425_result.xlsx
+++ b/FP425_result.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Turn on the ShowerHead</t>
+          <t>Put toiletpaper on the countertop</t>
         </is>
       </c>
       <c r="B2" t="n">
